--- a/storage/app/templates/timesheet_time.xlsx
+++ b/storage/app/templates/timesheet_time.xlsx
@@ -18,16 +18,14 @@
     <definedName name="thangdata2">[2]data2!$M$2:$M$25</definedName>
     <definedName name="thangdt">[2]data2!$P$2:$P$25</definedName>
     <definedName name="tienchiphi">[2]data!$F$2:$F$1015</definedName>
-    <definedName localSheetId="0" name="Thang">#REF!</definedName>
     <definedName name="ExpenseCategories">#REF!</definedName>
     <definedName name="Nam">#REF!</definedName>
-    <definedName localSheetId="0" name="ExpenseCategories">#REF!</definedName>
     <definedName name="Thang">#REF!</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="CpUruzMtnMqRBSKqbnsVo48rhZZm7RBy3Fmk+jNVioc="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="Xbw3a9WkPxclfsQVEbHfykgbpZP6ngh8aPvn3+rxA20="/>
     </ext>
   </extLst>
 </workbook>
@@ -718,7 +716,7 @@
       <xdr:row>2</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1171575" cy="561975"/>
+    <xdr:ext cx="1114425" cy="533400"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="0" name="image1.png" title="Hình ảnh"/>
@@ -997,8 +995,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
-    <tabColor rgb="FF92D050"/>
-    <pageSetUpPr/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
@@ -66291,12 +66288,6 @@
       <formula>AND(#REF!=TRUE,#REF!=1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins bottom="0.0" footer="0.0" header="0.0" left="0.0" right="0.0" top="0.0"/>
-  <pageSetup orientation="landscape"/>
-  <colBreaks count="1" manualBreakCount="1">
-    <brk id="71" man="1"/>
-  </colBreaks>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>